--- a/pneumatic_data.xlsx
+++ b/pneumatic_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\学校\毕设\我的\0314\Pneumatic_Selection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4C51AF-56D5-4A9E-ADF9-FF28A8440DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5810D38B-A185-4729-BBCD-6E87999DBCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F66809EE-D9B7-4651-B306-25BA8A37F87F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F66809EE-D9B7-4651-B306-25BA8A37F87F}"/>
   </bookViews>
   <sheets>
     <sheet name="Actuators" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="369">
   <si>
     <t>Standard</t>
   </si>
@@ -190,932 +190,1024 @@
     <t>Stroke: 100-5000mm</t>
   </si>
   <si>
+    <t>Rotary</t>
+  </si>
+  <si>
+    <t>Rack &amp; Pinion</t>
+  </si>
+  <si>
+    <t>10, 20, 30, 50</t>
+  </si>
+  <si>
+    <t>Angle: 0-190°</t>
+  </si>
+  <si>
+    <t>MHZ2</t>
+  </si>
+  <si>
+    <t>Gripper</t>
+  </si>
+  <si>
+    <t>Parallel Style</t>
+  </si>
+  <si>
+    <t>10, 16, 20, 25, 32, 40</t>
+  </si>
+  <si>
+    <t>Stroke: 4-22mm (Open)</t>
+  </si>
+  <si>
+    <t>平行二指气爪，最通用的机械手末端执行器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 侧面 / 底部安装 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>齿轮齿条式摆动气缸，用于工件翻转，角度可调</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械接合式无杆气缸，超长行程，节省轴向空间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三轴导杆气缸，滑动轴承耐冲击，适合推料 / 阻挡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 法兰安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 两端安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 螺钉调节</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>Voltage_Signal</t>
+  </si>
+  <si>
+    <t>Solenoid</t>
+  </si>
+  <si>
+    <t>Pilot Operated</t>
+  </si>
+  <si>
+    <t>DC24V, AC220V</t>
+  </si>
+  <si>
+    <t>M5, 1/8</t>
+  </si>
+  <si>
+    <t>全球主流紧凑型电磁阀，体积小流量大，集装式设计</t>
+  </si>
+  <si>
+    <t>4V210</t>
+  </si>
+  <si>
+    <t>1/8, 1/4</t>
+  </si>
+  <si>
+    <t>中国市场"面包阀"，便宜耐用，控制双作用气缸</t>
+  </si>
+  <si>
+    <t>4V230C</t>
+  </si>
+  <si>
+    <t>三位五通中封阀，用于气缸中途停止防止掉落</t>
+  </si>
+  <si>
+    <t>Proportional</t>
+  </si>
+  <si>
+    <t>Electro-Pneumatic</t>
+  </si>
+  <si>
+    <t>Pressure Control</t>
+  </si>
+  <si>
+    <t>0-10V, 4-20mA</t>
+  </si>
+  <si>
+    <t>电气比例阀，根据电信号无级调节气压，智能化控制核心</t>
+  </si>
+  <si>
+    <t>VM</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Plunger/Roller</t>
+  </si>
+  <si>
+    <t>2/3 Way</t>
+  </si>
+  <si>
+    <t>Manual Force</t>
+  </si>
+  <si>
+    <t>机械阀，通过滚轮或柱塞触发，无需用电</t>
+  </si>
+  <si>
+    <t>Direct Operated</t>
+  </si>
+  <si>
+    <t>直动式高频阀，可用于真空环境或单作用气缸</t>
+  </si>
+  <si>
+    <t>5/2, 5/3, 3/2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/2 Single/Double</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/3 Center Closed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/2Universal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/8, 1/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Filtration</t>
+  </si>
+  <si>
+    <t>Drain_Type</t>
+  </si>
+  <si>
+    <t>FRL Unit</t>
+  </si>
+  <si>
+    <t>5μm</t>
+  </si>
+  <si>
+    <t>Auto/Manual</t>
+  </si>
+  <si>
+    <t>1/4, 3/8, 1/2</t>
+  </si>
+  <si>
+    <t>模块化FRL组合(过滤+减压+油雾)，标准气源处理</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>40μm</t>
+  </si>
+  <si>
+    <t>Manual/Auto</t>
+  </si>
+  <si>
+    <t>1/4, 3/8</t>
+  </si>
+  <si>
+    <t>亚德客标准二联件，经济适用</t>
+  </si>
+  <si>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>Regulator</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>精密减压阀，用于需要高精度压力控制的张力系统</t>
+  </si>
+  <si>
+    <t>AFF</t>
+  </si>
+  <si>
+    <t>Main Filter</t>
+  </si>
+  <si>
+    <t>1μm</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>1/2 - 2</t>
+  </si>
+  <si>
+    <t>主管路过滤器，去除油雾和杂质</t>
+  </si>
+  <si>
+    <t>Spec_Key</t>
+  </si>
+  <si>
+    <t>Connection</t>
+  </si>
+  <si>
+    <t>Shape</t>
+  </si>
+  <si>
+    <t>Generator</t>
+  </si>
+  <si>
+    <t>Ejector System</t>
+  </si>
+  <si>
+    <t>Integrated</t>
+  </si>
+  <si>
+    <t>高端集成式真空发生器，集成了供给阀、破坏阀、过滤器</t>
+  </si>
+  <si>
+    <t>Box Type</t>
+  </si>
+  <si>
+    <t>Tube</t>
+  </si>
+  <si>
+    <t>基础管接式真空发生器，结构简单，利用文丘里效应</t>
+  </si>
+  <si>
+    <t>ZP3</t>
+  </si>
+  <si>
+    <t>Pad</t>
+  </si>
+  <si>
+    <t>Suction Cup</t>
+  </si>
+  <si>
+    <t>Adapter</t>
+  </si>
+  <si>
+    <t>Flat/Bellows</t>
+  </si>
+  <si>
+    <t>真空吸盘，平形吸钢板，风琴形吸软包装</t>
+  </si>
+  <si>
+    <t>OVEM</t>
+  </si>
+  <si>
+    <t>Smart Vacuum</t>
+  </si>
+  <si>
+    <t>智能真空发生器，带显示屏和IO-Link通讯</t>
+  </si>
+  <si>
+    <t>Output_Signal</t>
+  </si>
+  <si>
+    <t>Detect_Range</t>
+  </si>
+  <si>
+    <t>Applicable</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>2-wire Solid State</t>
+  </si>
+  <si>
+    <t>On/Off</t>
+  </si>
+  <si>
+    <t>SMC Cylinders</t>
+  </si>
+  <si>
+    <t>无触点磁性开关，直接安装型，检测活塞位置</t>
+  </si>
+  <si>
+    <t>Reed Switch</t>
+  </si>
+  <si>
+    <t>有触点舌簧开关，价格便宜</t>
+  </si>
+  <si>
+    <t>Pressure</t>
+  </si>
+  <si>
+    <t>NPN/PNP + Analog</t>
+  </si>
+  <si>
+    <t>-0.1 to 1.0 MPa</t>
+  </si>
+  <si>
+    <t>Air Lines</t>
+  </si>
+  <si>
+    <t>数字压力开关，双色显示，带模拟量输出</t>
+  </si>
+  <si>
+    <t>PFM7</t>
+  </si>
+  <si>
+    <t>Flow</t>
+  </si>
+  <si>
+    <t>Digital Output</t>
+  </si>
+  <si>
+    <t>10-1000 L/min</t>
+  </si>
+  <si>
+    <t>数字流量开关，监控系统耗气量和泄漏</t>
+  </si>
+  <si>
+    <t>MY1B</t>
+  </si>
+  <si>
+    <t>Mechanically Jointed</t>
+  </si>
+  <si>
+    <t>25-100</t>
+  </si>
+  <si>
+    <t>Basic, Foot</t>
+  </si>
+  <si>
+    <t>机械式无杆气缸，节省安装空间，适合超长行程传输</t>
+  </si>
+  <si>
+    <t>Table, Flange</t>
+  </si>
+  <si>
+    <t>CXS</t>
+  </si>
+  <si>
+    <t>Dual Rod</t>
+  </si>
+  <si>
+    <t>Slide Bearing</t>
+  </si>
+  <si>
+    <t>Stroke: 10-100mm</t>
+  </si>
+  <si>
+    <t>Basic, Bolt</t>
+  </si>
+  <si>
+    <t>双轴气缸，高抗扭矩能力，适合推举和定位，防止杆旋转</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>Twin Rod</t>
+  </si>
+  <si>
+    <t>Stroke: 10-200mm</t>
+  </si>
+  <si>
+    <t>Basic, Flange</t>
+  </si>
+  <si>
+    <t>亚德客双轴气缸，双活塞杆设计，抗弯曲抗扭转性能好</t>
+  </si>
+  <si>
+    <t>HFY</t>
+  </si>
+  <si>
+    <t>Stroke: 4-25mm</t>
+  </si>
+  <si>
+    <t>Side, Bottom</t>
+  </si>
+  <si>
+    <t>亚德客平行气爪，带滚珠导轨，高精度高刚性</t>
+  </si>
+  <si>
+    <t>RMS</t>
+  </si>
+  <si>
+    <t>Rotary Table</t>
+  </si>
+  <si>
+    <t>亚德客旋转气缸，带调节螺钉，内置磁环</t>
+  </si>
+  <si>
+    <t>6-32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10-50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SY5000</t>
+  </si>
+  <si>
+    <t>5/2 5/3</t>
+  </si>
+  <si>
+    <t>中型流量标准电磁阀，驱动40-63缸径气缸，可集装安装</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>Flow Control</t>
+  </si>
+  <si>
+    <t>Speed Controller</t>
+  </si>
+  <si>
+    <t>Throttle Valve</t>
+  </si>
+  <si>
+    <t>M5, 1/8, 1/4, 3/8</t>
+  </si>
+  <si>
+    <t>L型调速阀，直接安装在气缸接口上，控制气缸运行速度</t>
+  </si>
+  <si>
+    <t>4V310</t>
+  </si>
+  <si>
+    <t>5/2 Single</t>
+  </si>
+  <si>
+    <t>亚德客300系列，比210流量更大，适合驱动63-80缸径</t>
+  </si>
+  <si>
+    <t>3V210</t>
+  </si>
+  <si>
+    <t>3/2 NC/NO</t>
+  </si>
+  <si>
+    <t>两位三通电磁阀，用于控制单作用气缸或吹气回路</t>
+  </si>
+  <si>
+    <t>ASC</t>
+  </si>
+  <si>
+    <t>One-way Throttle</t>
+  </si>
+  <si>
+    <t>单向节流阀，管式安装，调节排气流量以控制速度</t>
+  </si>
+  <si>
+    <t>VHK</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>Finger Valve</t>
+  </si>
+  <si>
+    <t>4, 6, 8, 10mm</t>
+  </si>
+  <si>
+    <t>指动阀（手动开关），用于局部气路的快速通断控制</t>
+  </si>
+  <si>
+    <t>AV</t>
+  </si>
+  <si>
+    <t>Soft Start</t>
+  </si>
+  <si>
+    <t>Solenoid/Manual</t>
+  </si>
+  <si>
+    <t>软启动阀，通气时压力缓慢上升，防止气缸急速伸出造成事故</t>
+  </si>
+  <si>
+    <t>GFC</t>
+  </si>
+  <si>
+    <t>亚德客G系列二联件，外观更现代，带内置压力表</t>
+  </si>
+  <si>
+    <t>GPR</t>
+  </si>
+  <si>
+    <t>精密减压阀，低压控制灵敏度高，用于平衡装置或张力控制</t>
+  </si>
+  <si>
+    <t>IDG</t>
+  </si>
+  <si>
+    <t>Dryer</t>
+  </si>
+  <si>
+    <t>膜式空气干燥器，去除压缩空气中的水蒸气，无需电源</t>
+  </si>
+  <si>
+    <t>AD402</t>
+  </si>
+  <si>
+    <t>Drain</t>
+  </si>
+  <si>
+    <t>Float Type</t>
+  </si>
+  <si>
+    <t>3/8, 1/2</t>
+  </si>
+  <si>
+    <t>自动排水器，安装在管路低点，自动排出冷凝水</t>
+  </si>
+  <si>
+    <t>ZP2</t>
+  </si>
+  <si>
+    <t>Standard Pad</t>
+  </si>
+  <si>
+    <t>Vertical Entry</t>
+  </si>
+  <si>
+    <t>Flat/Ribbed</t>
+  </si>
+  <si>
+    <t>标准型真空吸盘，材质多样(NBR/硅胶)，通用性强</t>
+  </si>
+  <si>
+    <t>Heavy Duty</t>
+  </si>
+  <si>
+    <t>Plunger</t>
+  </si>
+  <si>
+    <t>Deep/Flat</t>
+  </si>
+  <si>
+    <t>重载吸盘，带缓冲弹簧杆，适合有高度差的工件抓取</t>
+  </si>
+  <si>
+    <t>Vertical</t>
+  </si>
+  <si>
+    <t>亚德客通用吸盘，性价比高，替换SMC对应型号</t>
+  </si>
+  <si>
+    <t>Ejector</t>
+  </si>
+  <si>
+    <t>Inline/Box</t>
+  </si>
+  <si>
+    <t>亚德客基本型真空发生器，管式连接，轻便易安装</t>
+  </si>
+  <si>
+    <t>0 to -101 kPa</t>
+  </si>
+  <si>
+    <t>Vacuum Lines</t>
+  </si>
+  <si>
+    <t>高精度真空压力开关，用于检测吸盘是否吸住工件</t>
+  </si>
+  <si>
+    <t>AirTAC Cylinders</t>
+  </si>
+  <si>
+    <t>亚德客标准有触点磁性开关，通用性强，LED指示灯</t>
+  </si>
+  <si>
+    <t>DMSG</t>
+  </si>
+  <si>
+    <t>Solid State</t>
+  </si>
+  <si>
+    <t>亚德客通用无触点开关，响应速度快，寿命长</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>Digital Pressure</t>
+  </si>
+  <si>
+    <t>NPN/PNP</t>
+  </si>
+  <si>
+    <t>Air/Vacuum</t>
+  </si>
+  <si>
+    <t>亚德客数字压力传感器，双画面显示，操作简单</t>
+  </si>
+  <si>
+    <t>CY1B</t>
+  </si>
+  <si>
+    <t>DRVS</t>
+  </si>
+  <si>
+    <t>HLQ</t>
+  </si>
+  <si>
+    <t>Slide Table</t>
+  </si>
+  <si>
+    <t>Magnetically Coupled</t>
+  </si>
+  <si>
+    <t>Vane</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>6-63</t>
+  </si>
+  <si>
+    <t>12-40</t>
+  </si>
+  <si>
+    <t>Stroke: 50-1000mm</t>
+  </si>
+  <si>
+    <t>Angle: 90/180/270</t>
+  </si>
+  <si>
+    <t>Stroke: 10-150mm</t>
+  </si>
+  <si>
+    <t>Direct Mount</t>
+  </si>
+  <si>
+    <t>Flange, Foot</t>
+  </si>
+  <si>
+    <t>Through Hole</t>
+  </si>
+  <si>
+    <t>磁耦合无杆气缸，行程极长且节省一半安装空间</t>
+  </si>
+  <si>
+    <t>半回转摆动气缸，用于工件翻转或分度盘驱动</t>
+  </si>
+  <si>
+    <t>高精度滑台气缸，自带直线导轨，抗侧向载荷能力极强</t>
+  </si>
+  <si>
+    <t>6-25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VTUG</t>
+  </si>
+  <si>
+    <t>Valve Island</t>
+  </si>
+  <si>
+    <t>Multipole/Fieldbus</t>
+  </si>
+  <si>
+    <t>5/2, 5/3, 3/2</t>
+  </si>
+  <si>
+    <t>DC24V</t>
+  </si>
+  <si>
+    <t>M5-1/4</t>
+  </si>
+  <si>
+    <t>紧凑型智能阀岛，支持PROFINET等总线通讯，大幅减少现场布线</t>
+  </si>
+  <si>
+    <t>EX250</t>
+  </si>
+  <si>
+    <t>Serial Transmission</t>
+  </si>
+  <si>
+    <t>Multiple</t>
+  </si>
+  <si>
+    <t>串行传输汇流板，高度模块化，最多可接32个电磁阀线圈</t>
+  </si>
+  <si>
+    <t>VEX</t>
+  </si>
+  <si>
+    <t>3 Port</t>
+  </si>
+  <si>
+    <t>大流量电气比例阀，用于精确且快速地控制大型气缸的压力或速度</t>
+  </si>
+  <si>
+    <t>KL</t>
+  </si>
+  <si>
+    <t>Fluid Control</t>
+  </si>
+  <si>
+    <t>Angle Seat</t>
+  </si>
+  <si>
+    <t>2/2 Way</t>
+  </si>
+  <si>
+    <t>Pneumatic Control</t>
+  </si>
+  <si>
+    <t>不锈钢角座阀，适用于水、蒸汽等大流量流体的高频启闭控制</t>
+  </si>
+  <si>
+    <t>Proportional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Regulator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/8-3/8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/8-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/8-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VBA</t>
+  </si>
+  <si>
+    <t>Booster</t>
+  </si>
+  <si>
+    <t>Pressure Multiplier</t>
+  </si>
+  <si>
+    <t>Max 2.0MPa</t>
+  </si>
+  <si>
+    <t>气动增压阀，无需纯电，纯靠气动将局部气路压力放大2-4倍</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>0.005-0.8MPa</t>
+  </si>
+  <si>
+    <t>高精密减压阀，压力波动极小，用于张力控制或测漏设备</t>
+  </si>
+  <si>
+    <t>AMH</t>
+  </si>
+  <si>
+    <t>Micro Filter</t>
+  </si>
+  <si>
+    <t>0.01μm</t>
+  </si>
+  <si>
+    <t>微雾分离器，提供超净气源，滤除99.9%的油雾和微小颗粒</t>
+  </si>
+  <si>
+    <t>1/4, 3/8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/4 - 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XT661</t>
+  </si>
+  <si>
+    <t>Bernoulli</t>
+  </si>
+  <si>
+    <t>Flat</t>
+  </si>
+  <si>
+    <t>伯努利悬浮吸盘，非接触式抓取，专用于易碎、极薄或多孔透气工件</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>Vacuum Filter</t>
+  </si>
+  <si>
+    <t>Inline</t>
+  </si>
+  <si>
+    <t>真空管路过滤器，串联在吸盘和发生器之间，防止粉尘吸入导致堵塞</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>Inline Ejector</t>
+  </si>
+  <si>
+    <t>High Vacuum</t>
+  </si>
+  <si>
+    <t>直通式真空发生器，体积如接头般小巧，直接安装在吸盘上方响应极快</t>
+  </si>
+  <si>
+    <t>3-wire Solid State</t>
+  </si>
+  <si>
+    <t>On/Off (2-color)</t>
+  </si>
+  <si>
+    <t>双色显示无触点磁性开关，处于最佳工作位置时亮绿灯，极大降低调试难度</t>
+  </si>
+  <si>
+    <t>D-MP</t>
+  </si>
+  <si>
+    <t>Analog/IO-Link</t>
+  </si>
+  <si>
+    <t>0-10V / 4-20mA</t>
+  </si>
+  <si>
+    <t>连续行程传感器，不仅给开关量，还能实时反馈气缸活塞的具体位移数值</t>
+  </si>
+  <si>
+    <t>SDAT</t>
+  </si>
+  <si>
+    <t>4-20mA</t>
+  </si>
+  <si>
+    <t>Festo Cylinders</t>
+  </si>
+  <si>
+    <t>T型槽位置变送器，精准监控执行元件运动轨迹</t>
+  </si>
+  <si>
+    <t>ZH(SMC)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZH(AT)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZPT(SMC)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZPT(AT)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D-M9B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adaptation_Relationship1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adaptation_Relationship2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adaptation_Relationship3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D-A93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D-M9NW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rodless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>MSQB</t>
-  </si>
-  <si>
-    <t>Rotary</t>
-  </si>
-  <si>
-    <t>Rack &amp; Pinion</t>
-  </si>
-  <si>
-    <t>10, 20, 30, 50</t>
-  </si>
-  <si>
-    <t>Angle: 0-190°</t>
-  </si>
-  <si>
-    <t>MHZ2</t>
-  </si>
-  <si>
-    <t>Gripper</t>
-  </si>
-  <si>
-    <t>Parallel Style</t>
-  </si>
-  <si>
-    <t>10, 16, 20, 25, 32, 40</t>
-  </si>
-  <si>
-    <t>Stroke: 4-22mm (Open)</t>
-  </si>
-  <si>
-    <t>平行二指气爪，最通用的机械手末端执行器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 侧面 / 底部安装 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>齿轮齿条式摆动气缸，用于工件翻转，角度可调</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机械接合式无杆气缸，超长行程，节省轴向空间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三轴导杆气缸，滑动轴承耐冲击，适合推料 / 阻挡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 法兰安装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 两端安装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 螺钉调节</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>Voltage_Signal</t>
-  </si>
-  <si>
-    <t>Solenoid</t>
-  </si>
-  <si>
-    <t>Pilot Operated</t>
-  </si>
-  <si>
-    <t>DC24V, AC220V</t>
-  </si>
-  <si>
-    <t>M5, 1/8</t>
-  </si>
-  <si>
-    <t>全球主流紧凑型电磁阀，体积小流量大，集装式设计</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS1-F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMSG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SY5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adaptation_Relationship4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4V210</t>
-  </si>
-  <si>
-    <t>1/8, 1/4</t>
-  </si>
-  <si>
-    <t>中国市场"面包阀"，便宜耐用，控制双作用气缸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SY3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adaptation_Relationship5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4V230C</t>
-  </si>
-  <si>
-    <t>三位五通中封阀，用于气缸中途停止防止掉落</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adaptation_Relationship6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZFA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZK2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OVEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZSE30A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VT307</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IDG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC-A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ISE30A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PFM7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ITV1000</t>
-  </si>
-  <si>
-    <t>Proportional</t>
-  </si>
-  <si>
-    <t>Electro-Pneumatic</t>
-  </si>
-  <si>
-    <t>Pressure Control</t>
-  </si>
-  <si>
-    <t>0-10V, 4-20mA</t>
-  </si>
-  <si>
-    <t>电气比例阀，根据电信号无级调节气压，智能化控制核心</t>
-  </si>
-  <si>
-    <t>VM</t>
-  </si>
-  <si>
-    <t>Mechanical</t>
-  </si>
-  <si>
-    <t>Plunger/Roller</t>
-  </si>
-  <si>
-    <t>2/3 Way</t>
-  </si>
-  <si>
-    <t>Manual Force</t>
-  </si>
-  <si>
-    <t>机械阀，通过滚轮或柱塞触发，无需用电</t>
-  </si>
-  <si>
-    <t>VT307</t>
-  </si>
-  <si>
-    <t>Direct Operated</t>
-  </si>
-  <si>
-    <t>直动式高频阀，可用于真空环境或单作用气缸</t>
-  </si>
-  <si>
-    <t>5/2, 5/3, 3/2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5/2 Single/Double</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5/3 Center Closed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3/2Universal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/8, 1/4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Filtration</t>
-  </si>
-  <si>
-    <t>Drain_Type</t>
-  </si>
-  <si>
-    <t>AC-A</t>
-  </si>
-  <si>
-    <t>FRL Unit</t>
-  </si>
-  <si>
-    <t>5μm</t>
-  </si>
-  <si>
-    <t>Auto/Manual</t>
-  </si>
-  <si>
-    <t>1/4, 3/8, 1/2</t>
-  </si>
-  <si>
-    <t>模块化FRL组合(过滤+减压+油雾)，标准气源处理</t>
-  </si>
-  <si>
-    <t>AC</t>
-  </si>
-  <si>
-    <t>40μm</t>
-  </si>
-  <si>
-    <t>Manual/Auto</t>
-  </si>
-  <si>
-    <t>1/4, 3/8</t>
-  </si>
-  <si>
-    <t>亚德客标准二联件，经济适用</t>
-  </si>
-  <si>
-    <t>IR</t>
-  </si>
-  <si>
-    <t>Regulator</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>精密减压阀，用于需要高精度压力控制的张力系统</t>
-  </si>
-  <si>
-    <t>AFF</t>
-  </si>
-  <si>
-    <t>Main Filter</t>
-  </si>
-  <si>
-    <t>1μm</t>
-  </si>
-  <si>
-    <t>Auto</t>
-  </si>
-  <si>
-    <t>1/2 - 2</t>
-  </si>
-  <si>
-    <t>主管路过滤器，去除油雾和杂质</t>
-  </si>
-  <si>
-    <t>Spec_Key</t>
-  </si>
-  <si>
-    <t>Connection</t>
-  </si>
-  <si>
-    <t>Shape</t>
-  </si>
-  <si>
-    <t>ZK2</t>
-  </si>
-  <si>
-    <t>Generator</t>
-  </si>
-  <si>
-    <t>Ejector System</t>
-  </si>
-  <si>
-    <t>Integrated</t>
-  </si>
-  <si>
-    <t>高端集成式真空发生器，集成了供给阀、破坏阀、过滤器</t>
-  </si>
-  <si>
-    <t>Box Type</t>
-  </si>
-  <si>
-    <t>Tube</t>
-  </si>
-  <si>
-    <t>基础管接式真空发生器，结构简单，利用文丘里效应</t>
-  </si>
-  <si>
-    <t>ZP3</t>
-  </si>
-  <si>
-    <t>Pad</t>
-  </si>
-  <si>
-    <t>Suction Cup</t>
-  </si>
-  <si>
-    <t>Adapter</t>
-  </si>
-  <si>
-    <t>Flat/Bellows</t>
-  </si>
-  <si>
-    <t>真空吸盘，平形吸钢板，风琴形吸软包装</t>
-  </si>
-  <si>
-    <t>OVEM</t>
-  </si>
-  <si>
-    <t>Smart Vacuum</t>
-  </si>
-  <si>
-    <t>智能真空发生器，带显示屏和IO-Link通讯</t>
-  </si>
-  <si>
-    <t>Output_Signal</t>
-  </si>
-  <si>
-    <t>Detect_Range</t>
-  </si>
-  <si>
-    <t>Applicable</t>
-  </si>
-  <si>
-    <t>D-M9B</t>
-  </si>
-  <si>
-    <t>Position</t>
-  </si>
-  <si>
-    <t>2-wire Solid State</t>
-  </si>
-  <si>
-    <t>On/Off</t>
-  </si>
-  <si>
-    <t>SMC Cylinders</t>
-  </si>
-  <si>
-    <t>无触点磁性开关，直接安装型，检测活塞位置</t>
-  </si>
-  <si>
-    <t>D-A93</t>
-  </si>
-  <si>
-    <t>Reed Switch</t>
-  </si>
-  <si>
-    <t>有触点舌簧开关，价格便宜</t>
-  </si>
-  <si>
-    <t>ISE30A</t>
-  </si>
-  <si>
-    <t>Pressure</t>
-  </si>
-  <si>
-    <t>NPN/PNP + Analog</t>
-  </si>
-  <si>
-    <t>-0.1 to 1.0 MPa</t>
-  </si>
-  <si>
-    <t>Air Lines</t>
-  </si>
-  <si>
-    <t>数字压力开关，双色显示，带模拟量输出</t>
-  </si>
-  <si>
-    <t>PFM7</t>
-  </si>
-  <si>
-    <t>Flow</t>
-  </si>
-  <si>
-    <t>Digital Output</t>
-  </si>
-  <si>
-    <t>10-1000 L/min</t>
-  </si>
-  <si>
-    <t>数字流量开关，监控系统耗气量和泄漏</t>
-  </si>
-  <si>
-    <t>MY1B</t>
-  </si>
-  <si>
-    <t>Mechanically Jointed</t>
-  </si>
-  <si>
-    <t>25-100</t>
-  </si>
-  <si>
-    <t>Basic, Foot</t>
-  </si>
-  <si>
-    <t>机械式无杆气缸，节省安装空间，适合超长行程传输</t>
-  </si>
-  <si>
-    <t>Table, Flange</t>
-  </si>
-  <si>
-    <t>CXS</t>
-  </si>
-  <si>
-    <t>Dual Rod</t>
-  </si>
-  <si>
-    <t>Slide Bearing</t>
-  </si>
-  <si>
-    <t>Stroke: 10-100mm</t>
-  </si>
-  <si>
-    <t>Basic, Bolt</t>
-  </si>
-  <si>
-    <t>双轴气缸，高抗扭矩能力，适合推举和定位，防止杆旋转</t>
-  </si>
-  <si>
-    <t>TN</t>
-  </si>
-  <si>
-    <t>Twin Rod</t>
-  </si>
-  <si>
-    <t>Stroke: 10-200mm</t>
-  </si>
-  <si>
-    <t>Basic, Flange</t>
-  </si>
-  <si>
-    <t>亚德客双轴气缸，双活塞杆设计，抗弯曲抗扭转性能好</t>
-  </si>
-  <si>
-    <t>HFY</t>
-  </si>
-  <si>
-    <t>Stroke: 4-25mm</t>
-  </si>
-  <si>
-    <t>Side, Bottom</t>
-  </si>
-  <si>
-    <t>亚德客平行气爪，带滚珠导轨，高精度高刚性</t>
-  </si>
-  <si>
-    <t>RMS</t>
-  </si>
-  <si>
-    <t>Rotary Table</t>
-  </si>
-  <si>
-    <t>亚德客旋转气缸，带调节螺钉，内置磁环</t>
-  </si>
-  <si>
-    <t>6-32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10-50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SY5000</t>
-  </si>
-  <si>
-    <t>5/2 5/3</t>
-  </si>
-  <si>
-    <t>中型流量标准电磁阀，驱动40-63缸径气缸，可集装安装</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>Flow Control</t>
-  </si>
-  <si>
-    <t>Speed Controller</t>
-  </si>
-  <si>
-    <t>Throttle Valve</t>
-  </si>
-  <si>
-    <t>M5, 1/8, 1/4, 3/8</t>
-  </si>
-  <si>
-    <t>L型调速阀，直接安装在气缸接口上，控制气缸运行速度</t>
-  </si>
-  <si>
-    <t>4V310</t>
-  </si>
-  <si>
-    <t>5/2 Single</t>
-  </si>
-  <si>
-    <t>亚德客300系列，比210流量更大，适合驱动63-80缸径</t>
-  </si>
-  <si>
-    <t>3V210</t>
-  </si>
-  <si>
-    <t>3/2 NC/NO</t>
-  </si>
-  <si>
-    <t>两位三通电磁阀，用于控制单作用气缸或吹气回路</t>
-  </si>
-  <si>
-    <t>ASC</t>
-  </si>
-  <si>
-    <t>One-way Throttle</t>
-  </si>
-  <si>
-    <t>单向节流阀，管式安装，调节排气流量以控制速度</t>
-  </si>
-  <si>
-    <t>VHK</t>
-  </si>
-  <si>
-    <t>Manual</t>
-  </si>
-  <si>
-    <t>Finger Valve</t>
-  </si>
-  <si>
-    <t>4, 6, 8, 10mm</t>
-  </si>
-  <si>
-    <t>指动阀（手动开关），用于局部气路的快速通断控制</t>
-  </si>
-  <si>
-    <t>AV</t>
-  </si>
-  <si>
-    <t>Soft Start</t>
-  </si>
-  <si>
-    <t>Solenoid/Manual</t>
-  </si>
-  <si>
-    <t>软启动阀，通气时压力缓慢上升，防止气缸急速伸出造成事故</t>
-  </si>
-  <si>
-    <t>GFC</t>
-  </si>
-  <si>
-    <t>亚德客G系列二联件，外观更现代，带内置压力表</t>
-  </si>
-  <si>
-    <t>GPR</t>
-  </si>
-  <si>
-    <t>精密减压阀，低压控制灵敏度高，用于平衡装置或张力控制</t>
-  </si>
-  <si>
-    <t>IDG</t>
-  </si>
-  <si>
-    <t>Dryer</t>
-  </si>
-  <si>
-    <t>膜式空气干燥器，去除压缩空气中的水蒸气，无需电源</t>
-  </si>
-  <si>
-    <t>AD402</t>
-  </si>
-  <si>
-    <t>Drain</t>
-  </si>
-  <si>
-    <t>Float Type</t>
-  </si>
-  <si>
-    <t>3/8, 1/2</t>
-  </si>
-  <si>
-    <t>自动排水器，安装在管路低点，自动排出冷凝水</t>
-  </si>
-  <si>
-    <t>ZP2</t>
-  </si>
-  <si>
-    <t>Standard Pad</t>
-  </si>
-  <si>
-    <t>Vertical Entry</t>
-  </si>
-  <si>
-    <t>Flat/Ribbed</t>
-  </si>
-  <si>
-    <t>标准型真空吸盘，材质多样(NBR/硅胶)，通用性强</t>
-  </si>
-  <si>
-    <t>Heavy Duty</t>
-  </si>
-  <si>
-    <t>Plunger</t>
-  </si>
-  <si>
-    <t>Deep/Flat</t>
-  </si>
-  <si>
-    <t>重载吸盘，带缓冲弹簧杆，适合有高度差的工件抓取</t>
-  </si>
-  <si>
-    <t>Vertical</t>
-  </si>
-  <si>
-    <t>亚德客通用吸盘，性价比高，替换SMC对应型号</t>
-  </si>
-  <si>
-    <t>Ejector</t>
-  </si>
-  <si>
-    <t>Inline/Box</t>
-  </si>
-  <si>
-    <t>亚德客基本型真空发生器，管式连接，轻便易安装</t>
-  </si>
-  <si>
-    <t>ZSE30A</t>
-  </si>
-  <si>
-    <t>0 to -101 kPa</t>
-  </si>
-  <si>
-    <t>Vacuum Lines</t>
-  </si>
-  <si>
-    <t>高精度真空压力开关，用于检测吸盘是否吸住工件</t>
-  </si>
-  <si>
-    <t>CS1-F</t>
-  </si>
-  <si>
-    <t>AirTAC Cylinders</t>
-  </si>
-  <si>
-    <t>亚德客标准有触点磁性开关，通用性强，LED指示灯</t>
-  </si>
-  <si>
-    <t>DMSG</t>
-  </si>
-  <si>
-    <t>Solid State</t>
-  </si>
-  <si>
-    <t>亚德客通用无触点开关，响应速度快，寿命长</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>Digital Pressure</t>
-  </si>
-  <si>
-    <t>NPN/PNP</t>
-  </si>
-  <si>
-    <t>Air/Vacuum</t>
-  </si>
-  <si>
-    <t>亚德客数字压力传感器，双画面显示，操作简单</t>
-  </si>
-  <si>
-    <t>CY1B</t>
-  </si>
-  <si>
-    <t>DRVS</t>
-  </si>
-  <si>
-    <t>HLQ</t>
-  </si>
-  <si>
-    <t>Slide Table</t>
-  </si>
-  <si>
-    <t>Magnetically Coupled</t>
-  </si>
-  <si>
-    <t>Vane</t>
-  </si>
-  <si>
-    <t>Precision</t>
-  </si>
-  <si>
-    <t>6-63</t>
-  </si>
-  <si>
-    <t>12-40</t>
-  </si>
-  <si>
-    <t>Stroke: 50-1000mm</t>
-  </si>
-  <si>
-    <t>Angle: 90/180/270</t>
-  </si>
-  <si>
-    <t>Stroke: 10-150mm</t>
-  </si>
-  <si>
-    <t>Direct Mount</t>
-  </si>
-  <si>
-    <t>Flange, Foot</t>
-  </si>
-  <si>
-    <t>Through Hole</t>
-  </si>
-  <si>
-    <t>磁耦合无杆气缸，行程极长且节省一半安装空间</t>
-  </si>
-  <si>
-    <t>半回转摆动气缸，用于工件翻转或分度盘驱动</t>
-  </si>
-  <si>
-    <t>高精度滑台气缸，自带直线导轨，抗侧向载荷能力极强</t>
-  </si>
-  <si>
-    <t>6-25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VTUG</t>
-  </si>
-  <si>
-    <t>Valve Island</t>
-  </si>
-  <si>
-    <t>Multipole/Fieldbus</t>
-  </si>
-  <si>
-    <t>5/2, 5/3, 3/2</t>
-  </si>
-  <si>
-    <t>DC24V</t>
-  </si>
-  <si>
-    <t>M5-1/4</t>
-  </si>
-  <si>
-    <t>紧凑型智能阀岛，支持PROFINET等总线通讯，大幅减少现场布线</t>
-  </si>
-  <si>
-    <t>EX250</t>
-  </si>
-  <si>
-    <t>Serial Transmission</t>
-  </si>
-  <si>
-    <t>Multiple</t>
-  </si>
-  <si>
-    <t>串行传输汇流板，高度模块化，最多可接32个电磁阀线圈</t>
-  </si>
-  <si>
-    <t>VEX</t>
-  </si>
-  <si>
-    <t>3 Port</t>
-  </si>
-  <si>
-    <t>大流量电气比例阀，用于精确且快速地控制大型气缸的压力或速度</t>
-  </si>
-  <si>
-    <t>KL</t>
-  </si>
-  <si>
-    <t>Fluid Control</t>
-  </si>
-  <si>
-    <t>Angle Seat</t>
-  </si>
-  <si>
-    <t>2/2 Way</t>
-  </si>
-  <si>
-    <t>Pneumatic Control</t>
-  </si>
-  <si>
-    <t>不锈钢角座阀，适用于水、蒸汽等大流量流体的高频启闭控制</t>
-  </si>
-  <si>
-    <t>Proportional</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Regulator</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/8-3/8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/8-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3/8-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>VBA</t>
-  </si>
-  <si>
-    <t>Booster</t>
-  </si>
-  <si>
-    <t>Pressure Multiplier</t>
-  </si>
-  <si>
-    <t>Max 2.0MPa</t>
-  </si>
-  <si>
-    <t>气动增压阀，无需纯电，纯靠气动将局部气路压力放大2-4倍</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>0.005-0.8MPa</t>
-  </si>
-  <si>
-    <t>高精密减压阀，压力波动极小，用于张力控制或测漏设备</t>
-  </si>
-  <si>
-    <t>AMH</t>
-  </si>
-  <si>
-    <t>Micro Filter</t>
-  </si>
-  <si>
-    <t>0.01μm</t>
-  </si>
-  <si>
-    <t>微雾分离器，提供超净气源，滤除99.9%的油雾和微小颗粒</t>
-  </si>
-  <si>
-    <t>1/4, 3/8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/4 - 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>XT661</t>
-  </si>
-  <si>
-    <t>Bernoulli</t>
-  </si>
-  <si>
-    <t>Flat</t>
-  </si>
-  <si>
-    <t>伯努利悬浮吸盘，非接触式抓取，专用于易碎、极薄或多孔透气工件</t>
-  </si>
-  <si>
-    <t>ZFA</t>
-  </si>
-  <si>
-    <t>Filter</t>
-  </si>
-  <si>
-    <t>Vacuum Filter</t>
-  </si>
-  <si>
-    <t>Inline</t>
-  </si>
-  <si>
-    <t>真空管路过滤器，串联在吸盘和发生器之间，防止粉尘吸入导致堵塞</t>
-  </si>
-  <si>
-    <t>VN</t>
-  </si>
-  <si>
-    <t>Inline Ejector</t>
-  </si>
-  <si>
-    <t>High Vacuum</t>
-  </si>
-  <si>
-    <t>直通式真空发生器，体积如接头般小巧，直接安装在吸盘上方响应极快</t>
-  </si>
-  <si>
-    <t>D-M9NW</t>
-  </si>
-  <si>
-    <t>3-wire Solid State</t>
-  </si>
-  <si>
-    <t>On/Off (2-color)</t>
-  </si>
-  <si>
-    <t>双色显示无触点磁性开关，处于最佳工作位置时亮绿灯，极大降低调试难度</t>
-  </si>
-  <si>
-    <t>D-MP</t>
-  </si>
-  <si>
-    <t>Analog/IO-Link</t>
-  </si>
-  <si>
-    <t>0-10V / 4-20mA</t>
-  </si>
-  <si>
-    <t>连续行程传感器，不仅给开关量，还能实时反馈气缸活塞的具体位移数值</t>
-  </si>
-  <si>
-    <t>SDAT</t>
-  </si>
-  <si>
-    <t>4-20mA</t>
-  </si>
-  <si>
-    <t>Festo Cylinders</t>
-  </si>
-  <si>
-    <t>T型槽位置变送器，精准监控执行元件运动轨迹</t>
-  </si>
-  <si>
-    <t>ZH(SMC)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZH(AT)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZPT(SMC)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ZPT(AT)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1497,17 +1589,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA147BF9-70D6-4D15-BB3E-E20D913D64BE}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="3" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="31.21875" customWidth="1"/>
-    <col min="6" max="6" width="22.88671875" customWidth="1"/>
-    <col min="7" max="7" width="38.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" customWidth="1"/>
+    <col min="8" max="8" width="51.6640625" customWidth="1"/>
+    <col min="9" max="9" width="29.44140625" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="27.109375" customWidth="1"/>
+    <col min="12" max="12" width="28.21875" customWidth="1"/>
+    <col min="13" max="13" width="23.33203125" customWidth="1"/>
+    <col min="14" max="14" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -1532,8 +1631,26 @@
       <c r="H1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>338</v>
+      </c>
+      <c r="J1" t="s">
+        <v>339</v>
+      </c>
+      <c r="K1" t="s">
+        <v>340</v>
+      </c>
+      <c r="L1" t="s">
+        <v>348</v>
+      </c>
+      <c r="M1" t="s">
+        <v>351</v>
+      </c>
+      <c r="N1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1558,8 +1675,26 @@
       <c r="H2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K2" t="s">
+        <v>342</v>
+      </c>
+      <c r="L2" t="s">
+        <v>347</v>
+      </c>
+      <c r="M2" t="s">
+        <v>352</v>
+      </c>
+      <c r="N2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1584,8 +1719,20 @@
       <c r="H3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K3" t="s">
+        <v>349</v>
+      </c>
+      <c r="L3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1610,8 +1757,11 @@
       <c r="H4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1636,8 +1786,17 @@
       <c r="H5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>337</v>
+      </c>
+      <c r="J5" t="s">
+        <v>342</v>
+      </c>
+      <c r="K5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1662,8 +1821,17 @@
       <c r="H6" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>345</v>
+      </c>
+      <c r="J6" t="s">
+        <v>346</v>
+      </c>
+      <c r="K6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1683,13 +1851,19 @@
         <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="I7" t="s">
+        <v>337</v>
+      </c>
+      <c r="J7" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1697,7 +1871,7 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>343</v>
       </c>
       <c r="D8" t="s">
         <v>46</v>
@@ -1709,114 +1883,126 @@
         <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="I8" t="s">
+        <v>337</v>
+      </c>
+      <c r="J8" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C9" t="s">
         <v>49</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>50</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>51</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>52</v>
       </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>337</v>
+      </c>
+      <c r="J9" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
         <v>54</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>55</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>56</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>57</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" t="s">
         <v>58</v>
       </c>
-      <c r="G10" t="s">
-        <v>60</v>
-      </c>
-      <c r="H10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C11" t="s">
         <v>45</v>
       </c>
       <c r="D11" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="E11" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F11" t="s">
         <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1824,30 +2010,30 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1855,30 +2041,30 @@
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1886,30 +2072,30 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1917,30 +2103,30 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1948,25 +2134,25 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1974,25 +2160,25 @@
         <v>19</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -2012,6 +2198,7 @@
     <col min="5" max="5" width="27.21875" customWidth="1"/>
     <col min="6" max="6" width="22.109375" customWidth="1"/>
     <col min="7" max="7" width="21.77734375" customWidth="1"/>
+    <col min="8" max="9" width="52.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2028,16 +2215,19 @@
         <v>6</v>
       </c>
       <c r="E1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" t="s">
         <v>67</v>
-      </c>
-      <c r="F1" t="s">
-        <v>68</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
       </c>
       <c r="H1" t="s">
         <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -2048,22 +2238,22 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
         <v>69</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F2" t="s">
         <v>70</v>
       </c>
-      <c r="E2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>71</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>72</v>
-      </c>
-      <c r="H2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2071,25 +2261,25 @@
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
         <v>69</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" t="s">
         <v>70</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>95</v>
       </c>
-      <c r="F3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" t="s">
-        <v>98</v>
-      </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2097,25 +2287,25 @@
         <v>19</v>
       </c>
       <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H4" t="s">
         <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -2123,25 +2313,25 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s">
         <v>79</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>80</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>81</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" t="s">
         <v>82</v>
-      </c>
-      <c r="F5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -2149,25 +2339,25 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
         <v>85</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>86</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>87</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" t="s">
         <v>88</v>
-      </c>
-      <c r="F6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H6" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -2175,25 +2365,28 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>360</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>93</v>
+        <v>90</v>
+      </c>
+      <c r="I7" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2201,25 +2394,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -2231,25 +2424,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -2261,25 +2454,25 @@
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -2291,25 +2484,25 @@
         <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -2321,25 +2514,25 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -2351,25 +2544,25 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -2381,25 +2574,25 @@
         <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -2411,25 +2604,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -2441,25 +2634,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -2471,25 +2664,25 @@
         <v>19</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="H17" s="3" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -2743,17 +2936,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E13665EC-A86D-4BD3-A3A6-78629AEC4B40}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.77734375" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="15.44140625" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" customWidth="1"/>
+    <col min="6" max="6" width="19.88671875" customWidth="1"/>
+    <col min="7" max="7" width="55" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="23.44140625" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" customWidth="1"/>
+    <col min="11" max="11" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2761,13 +2958,13 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F1" t="s">
         <v>2</v>
@@ -2775,325 +2972,364 @@
       <c r="G1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I1" t="s">
+        <v>339</v>
+      </c>
+      <c r="J1" t="s">
+        <v>340</v>
+      </c>
+      <c r="K1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" t="s">
         <v>103</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>104</v>
       </c>
-      <c r="D2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>363</v>
+      </c>
+      <c r="I2" t="s">
+        <v>364</v>
+      </c>
+      <c r="J2" t="s">
+        <v>365</v>
+      </c>
+      <c r="K2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
       <c r="B3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" t="s">
         <v>109</v>
       </c>
-      <c r="C3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>359</v>
+      </c>
+      <c r="I3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="H4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" t="s">
         <v>118</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
         <v>119</v>
       </c>
-      <c r="D5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="H7" s="1"/>
+        <v>214</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>367</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="H8" s="1"/>
+        <v>216</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>368</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H9" s="1"/>
+        <v>219</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>362</v>
+      </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>310</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>116</v>
+        <v>308</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>313</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>116</v>
+        <v>309</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>317</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -3107,7 +3343,7 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -3121,7 +3357,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -3251,6 +3487,12 @@
     <col min="4" max="4" width="17.109375" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="7" max="7" width="63.33203125" customWidth="1"/>
+    <col min="8" max="8" width="26.88671875" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" customWidth="1"/>
+    <col min="10" max="10" width="25.6640625" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -3264,16 +3506,34 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I1" t="s">
+        <v>339</v>
+      </c>
+      <c r="J1" t="s">
+        <v>340</v>
+      </c>
+      <c r="K1" t="s">
+        <v>348</v>
+      </c>
+      <c r="L1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M1" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -3281,22 +3541,25 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>356</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G2" t="s">
-        <v>131</v>
+        <v>126</v>
+      </c>
+      <c r="H2" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -3304,22 +3567,25 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" t="s">
         <v>128</v>
       </c>
-      <c r="D3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" t="s">
-        <v>133</v>
-      </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>134</v>
+        <v>129</v>
+      </c>
+      <c r="H3" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -3327,22 +3593,31 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" t="s">
         <v>135</v>
       </c>
-      <c r="C4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G4" t="s">
-        <v>140</v>
+      <c r="H4" t="s">
+        <v>355</v>
+      </c>
+      <c r="I4" t="s">
+        <v>356</v>
+      </c>
+      <c r="J4" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -3350,22 +3625,22 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G5" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -3373,24 +3648,26 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="H6" s="1"/>
+        <v>229</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -3402,24 +3679,26 @@
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H7" s="1"/>
+        <v>233</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -3431,24 +3710,26 @@
         <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="H8" s="1"/>
+        <v>235</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -3460,24 +3741,26 @@
         <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H9" s="1"/>
+        <v>238</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>359</v>
+      </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -3489,24 +3772,26 @@
         <v>13</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H10" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -3517,25 +3802,29 @@
         <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+        <v>317</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>334</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -3545,22 +3834,22 @@
         <v>25</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -3765,13 +4054,13 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -3782,22 +4071,22 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>337</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -3805,22 +4094,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>341</v>
       </c>
       <c r="C3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" t="s">
         <v>148</v>
-      </c>
-      <c r="D3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -3828,22 +4117,22 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>364</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -3851,22 +4140,22 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F5" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="G5" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -3874,22 +4163,22 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>247</v>
+        <v>358</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -3902,22 +4191,22 @@
         <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>251</v>
+        <v>345</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -3930,22 +4219,22 @@
         <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -3958,22 +4247,22 @@
         <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -3986,22 +4275,22 @@
         <v>13</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -4013,22 +4302,22 @@
         <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -4040,22 +4329,22 @@
         <v>25</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
